--- a/base_datas/crescimento_medio_receita_porte.xlsx
+++ b/base_datas/crescimento_medio_receita_porte.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>334.7053469608703</v>
+        <v>365.170768643801</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>269.31726796071</v>
+        <v>288.6208745049647</v>
       </c>
     </row>
     <row r="4">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>327.7652772277014</v>
+        <v>353.1633725992844</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>230.9704172252606</v>
+        <v>239.7635833334444</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>311.1715834413913</v>
+        <v>339.5332703019551</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>316.9611158798973</v>
+        <v>343.2118929331372</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>188.0636851612606</v>
+        <v>192.5167057231293</v>
       </c>
     </row>
     <row r="9">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>313.2742100409947</v>
+        <v>340.9282456257582</v>
       </c>
     </row>
   </sheetData>
